--- a/parafit_summary_cosp.xlsx
+++ b/parafit_summary_cosp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,67 +485,89 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Coala_Cosp</t>
+          <t>Asymmetree_Cosp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>114856120.66</v>
+        <v>6346.29</v>
       </c>
       <c r="C3" t="n">
-        <v>441664692.97</v>
+        <v>6565.9</v>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>496</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Real_Data</t>
+          <t>Coala_Cosp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15807.72</v>
+        <v>114856120.66</v>
       </c>
       <c r="C4" t="n">
-        <v>21682.83</v>
+        <v>441664692.97</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>495</v>
       </c>
       <c r="F4" t="n">
-        <v>60.87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Real_Data</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15807.72</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21682.83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56.52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>Treeducken_Cosp</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>4831.76</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>11404.17</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>497</v>
       </c>
-      <c r="E5" t="n">
-        <v>424</v>
-      </c>
-      <c r="F5" t="n">
-        <v>85.31</v>
+      <c r="E6" t="n">
+        <v>425</v>
+      </c>
+      <c r="F6" t="n">
+        <v>85.51000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/parafit_summary_cosp.xlsx
+++ b/parafit_summary_cosp.xlsx
@@ -476,10 +476,10 @@
         <v>191</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>29.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6346.29</v>
+        <v>16350.03</v>
       </c>
       <c r="C3" t="n">
-        <v>6565.9</v>
+        <v>15027.43</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>500</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15807.72</v>
+        <v>205038484.64</v>
       </c>
       <c r="C5" t="n">
-        <v>21682.83</v>
+        <v>1164019159.73</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>56.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>497</v>
       </c>
       <c r="E6" t="n">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>85.51000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
